--- a/Grafico di Gantt.xlsx
+++ b/Grafico di Gantt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\dashboard\ProgettoRobot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37AB52D-F946-459D-9E06-497505FC6D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC0EFC8-F916-4482-ACA8-84BE8B828C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="55">
   <si>
     <t>GRAFICO DI GANTT</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>Test codice</t>
+  </si>
+  <si>
+    <t>Barchi - Gabanella-Visentin</t>
   </si>
 </sst>
 </file>
@@ -1114,6 +1117,9 @@
     <xf numFmtId="14" fontId="21" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="21" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1134,23 +1140,20 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1605,14 +1608,14 @@
     </row>
     <row r="2" spans="1:98" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
@@ -1620,39 +1623,39 @@
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="95"/>
-      <c r="W2" s="97"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="95"/>
-      <c r="Z2" s="95"/>
-      <c r="AA2" s="95"/>
-      <c r="AB2" s="95"/>
-      <c r="AC2" s="95"/>
-      <c r="AD2" s="95"/>
-      <c r="AE2" s="95"/>
-      <c r="AF2" s="95"/>
-      <c r="AG2" s="95"/>
-      <c r="AH2" s="95"/>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="95"/>
-      <c r="AK2" s="95"/>
-      <c r="AL2" s="95"/>
-      <c r="AM2" s="95"/>
-      <c r="AN2" s="95"/>
-      <c r="AO2" s="95"/>
-      <c r="AP2" s="95"/>
-      <c r="AQ2" s="95"/>
-      <c r="AR2" s="95"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="95"/>
-      <c r="AU2" s="95"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="96"/>
+      <c r="U2" s="96"/>
+      <c r="V2" s="96"/>
+      <c r="W2" s="98"/>
+      <c r="X2" s="96"/>
+      <c r="Y2" s="96"/>
+      <c r="Z2" s="96"/>
+      <c r="AA2" s="96"/>
+      <c r="AB2" s="96"/>
+      <c r="AC2" s="96"/>
+      <c r="AD2" s="96"/>
+      <c r="AE2" s="96"/>
+      <c r="AF2" s="96"/>
+      <c r="AG2" s="96"/>
+      <c r="AH2" s="96"/>
+      <c r="AI2" s="96"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="96"/>
+      <c r="AL2" s="96"/>
+      <c r="AM2" s="96"/>
+      <c r="AN2" s="96"/>
+      <c r="AO2" s="96"/>
+      <c r="AP2" s="96"/>
+      <c r="AQ2" s="96"/>
+      <c r="AR2" s="96"/>
+      <c r="AS2" s="96"/>
+      <c r="AT2" s="96"/>
+      <c r="AU2" s="96"/>
       <c r="AV2" s="11"/>
       <c r="AW2" s="11"/>
       <c r="AX2" s="11"/>
@@ -1805,18 +1808,18 @@
       <c r="CS3" s="1"/>
       <c r="CT3" s="1"/>
     </row>
-    <row r="4" spans="1:98" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:98" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1"/>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100" t="s">
+      <c r="C4" s="100"/>
+      <c r="D4" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
@@ -1824,36 +1827,36 @@
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
-      <c r="O4" s="98" t="s">
+      <c r="O4" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="99"/>
-      <c r="X4" s="101" t="s">
+      <c r="P4" s="100"/>
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="100"/>
+      <c r="W4" s="100"/>
+      <c r="X4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="99"/>
-      <c r="AA4" s="99"/>
-      <c r="AB4" s="99"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="99"/>
-      <c r="AE4" s="99"/>
-      <c r="AF4" s="99"/>
-      <c r="AG4" s="99"/>
-      <c r="AH4" s="99"/>
-      <c r="AI4" s="99"/>
-      <c r="AJ4" s="99"/>
-      <c r="AK4" s="99"/>
-      <c r="AL4" s="99"/>
-      <c r="AM4" s="99"/>
-      <c r="AN4" s="99"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
+      <c r="AC4" s="100"/>
+      <c r="AD4" s="100"/>
+      <c r="AE4" s="100"/>
+      <c r="AF4" s="100"/>
+      <c r="AG4" s="100"/>
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="100"/>
+      <c r="AK4" s="100"/>
+      <c r="AL4" s="100"/>
+      <c r="AM4" s="100"/>
+      <c r="AN4" s="100"/>
       <c r="AO4" s="17"/>
       <c r="AP4" s="9"/>
       <c r="AQ4" s="9"/>
@@ -1913,18 +1916,18 @@
       <c r="CS4" s="1"/>
       <c r="CT4" s="1"/>
     </row>
-    <row r="5" spans="1:98" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:98" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="1"/>
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="103" t="s">
+      <c r="C5" s="100"/>
+      <c r="D5" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -1932,35 +1935,35 @@
       <c r="L5" s="16"/>
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
-      <c r="O5" s="98" t="s">
+      <c r="O5" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
-      <c r="W5" s="99"/>
-      <c r="X5" s="104">
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="100"/>
+      <c r="U5" s="100"/>
+      <c r="V5" s="100"/>
+      <c r="W5" s="100"/>
+      <c r="X5" s="103">
         <v>46083</v>
       </c>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="99"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
-      <c r="AH5" s="99"/>
-      <c r="AI5" s="99"/>
-      <c r="AJ5" s="99"/>
-      <c r="AK5" s="99"/>
-      <c r="AL5" s="99"/>
-      <c r="AM5" s="99"/>
+      <c r="Y5" s="100"/>
+      <c r="Z5" s="100"/>
+      <c r="AA5" s="100"/>
+      <c r="AB5" s="100"/>
+      <c r="AC5" s="100"/>
+      <c r="AD5" s="100"/>
+      <c r="AE5" s="100"/>
+      <c r="AF5" s="100"/>
+      <c r="AG5" s="100"/>
+      <c r="AH5" s="100"/>
+      <c r="AI5" s="100"/>
+      <c r="AJ5" s="100"/>
+      <c r="AK5" s="100"/>
+      <c r="AL5" s="100"/>
+      <c r="AM5" s="100"/>
       <c r="AN5" s="18"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="1"/>
@@ -2223,19 +2226,19 @@
     </row>
     <row r="8" spans="1:98" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23"/>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="102" t="s">
+      <c r="D8" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="102" t="s">
+      <c r="F8" s="104" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="86" t="s">
@@ -2394,7 +2397,7 @@
       <c r="AN9" s="83"/>
       <c r="AO9" s="83"/>
       <c r="AP9" s="85"/>
-      <c r="AQ9" s="107">
+      <c r="AQ9" s="94">
         <v>46062</v>
       </c>
       <c r="AR9" s="83"/>
@@ -2403,7 +2406,7 @@
       <c r="AU9" s="83"/>
       <c r="AV9" s="83"/>
       <c r="AW9" s="85"/>
-      <c r="AX9" s="107">
+      <c r="AX9" s="94">
         <v>46069</v>
       </c>
       <c r="AY9" s="83"/>
@@ -2412,7 +2415,7 @@
       <c r="BB9" s="83"/>
       <c r="BC9" s="83"/>
       <c r="BD9" s="85"/>
-      <c r="BE9" s="107">
+      <c r="BE9" s="94">
         <v>46076</v>
       </c>
       <c r="BF9" s="83"/>
@@ -2421,7 +2424,7 @@
       <c r="BI9" s="83"/>
       <c r="BJ9" s="83"/>
       <c r="BK9" s="84"/>
-      <c r="BL9" s="107">
+      <c r="BL9" s="94">
         <v>46083</v>
       </c>
       <c r="BM9" s="83"/>
@@ -2430,7 +2433,7 @@
       <c r="BP9" s="83"/>
       <c r="BQ9" s="83"/>
       <c r="BR9" s="84"/>
-      <c r="BS9" s="107">
+      <c r="BS9" s="94">
         <v>46090</v>
       </c>
       <c r="BT9" s="83"/>
@@ -3974,7 +3977,7 @@
         <v>48</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E22" s="48">
         <v>46076</v>
@@ -4087,7 +4090,7 @@
         <v>50</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E23" s="48">
         <v>46083</v>
